--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486839_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486839_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.145899999999999</v>
+        <v>9.7293</v>
       </c>
       <c r="E2" t="n">
-        <v>6.8823</v>
+        <v>7.1925</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2636</v>
+        <v>2.5368</v>
       </c>
       <c r="G2" t="n">
         <v>8.563599999999999</v>
@@ -610,13 +610,13 @@
         <v>1.9308</v>
       </c>
       <c r="S2" t="n">
-        <v>0.32</v>
+        <v>0.9034</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1933</v>
+        <v>0.117</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5133</v>
+        <v>0.7865</v>
       </c>
       <c r="V2" t="n">
         <v>1.2277</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.8815</v>
+        <v>5.8</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1602</v>
+        <v>2.7807</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7213</v>
+        <v>3.0193</v>
       </c>
       <c r="G3" t="n">
         <v>0.8208</v>
@@ -688,13 +688,13 @@
         <v>2.51</v>
       </c>
       <c r="S3" t="n">
-        <v>0.0608</v>
+        <v>0.9792999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.6071</v>
+        <v>0.0134</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6679</v>
+        <v>0.9659</v>
       </c>
       <c r="V3" t="n">
         <v>2.4554</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.831</v>
+        <v>5.162</v>
       </c>
       <c r="E4" t="n">
-        <v>3.7841</v>
+        <v>3.9909</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0469</v>
+        <v>1.1711</v>
       </c>
       <c r="G4" t="n">
         <v>3.2602</v>
@@ -766,13 +766,13 @@
         <v>2.51</v>
       </c>
       <c r="S4" t="n">
-        <v>0.331</v>
+        <v>0.662</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.221</v>
+        <v>-0.0141</v>
       </c>
       <c r="U4" t="n">
-        <v>0.552</v>
+        <v>0.6762</v>
       </c>
       <c r="V4" t="n">
         <v>-1.2703</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.9127</v>
+        <v>2.3129</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6768999999999999</v>
+        <v>-0.3021</v>
       </c>
       <c r="F5" t="n">
-        <v>3.2358</v>
+        <v>2.615</v>
       </c>
       <c r="G5" t="n">
         <v>0.1517</v>
@@ -844,13 +844,13 @@
         <v>1.5446</v>
       </c>
       <c r="S5" t="n">
-        <v>4.4134</v>
+        <v>2.8136</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1508</v>
+        <v>1.1718</v>
       </c>
       <c r="U5" t="n">
-        <v>2.2626</v>
+        <v>1.6418</v>
       </c>
       <c r="V5" t="n">
         <v>0.6991000000000001</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.4874</v>
+        <v>2.0311</v>
       </c>
       <c r="E6" t="n">
-        <v>2.8315</v>
+        <v>1.7973</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6559</v>
+        <v>0.2337</v>
       </c>
       <c r="G6" t="n">
         <v>1.0516</v>
@@ -922,13 +922,13 @@
         <v>1.5446</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7528</v>
+        <v>1.2964</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8751</v>
+        <v>0.8409</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8776</v>
+        <v>0.4555</v>
       </c>
       <c r="V6" t="n">
         <v>1.2277</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.2156</v>
+        <v>1.1659</v>
       </c>
       <c r="E7" t="n">
         <v>-0.2267</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4423</v>
+        <v>1.3926</v>
       </c>
       <c r="G7" t="n">
         <v>0.8981</v>
@@ -1000,13 +1000,13 @@
         <v>1.7377</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1324</v>
+        <v>0.0828</v>
       </c>
       <c r="T7" t="n">
         <v>0.0274</v>
       </c>
       <c r="U7" t="n">
-        <v>0.105</v>
+        <v>0.0554</v>
       </c>
       <c r="V7" t="n">
         <v>0.5712</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4279</v>
+        <v>0.8141</v>
       </c>
       <c r="E8" t="n">
-        <v>1.972</v>
+        <v>2.2341</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.5442</v>
+        <v>-1.42</v>
       </c>
       <c r="G8" t="n">
         <v>-0.4023</v>
@@ -1078,13 +1078,13 @@
         <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>0.7723</v>
+        <v>1.1584</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5515</v>
+        <v>0.8135</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2208</v>
+        <v>0.3449</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3282</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.5404</v>
+        <v>-0.2039</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1613</v>
+        <v>0.1008</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.3791</v>
+        <v>-0.3047</v>
       </c>
       <c r="G9" t="n">
         <v>-2.3137</v>
@@ -1156,13 +1156,13 @@
         <v>1.9308</v>
       </c>
       <c r="S9" t="n">
-        <v>1.2633</v>
+        <v>1.5998</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5237000000000001</v>
+        <v>0.7857</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7396</v>
+        <v>0.8141</v>
       </c>
       <c r="V9" t="n">
         <v>-1.2277</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.8412</v>
+        <v>-2.5999</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6272</v>
+        <v>-2.2618</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.214</v>
+        <v>-0.3381</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3518</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4414</v>
+        <v>0.6827</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0277</v>
+        <v>0.3378</v>
       </c>
       <c r="U10" t="n">
-        <v>0.469</v>
+        <v>0.3449</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.0588</v>
+        <v>-4.4739</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9777</v>
+        <v>-1.7157</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.0811</v>
+        <v>-2.7583</v>
       </c>
       <c r="G11" t="n">
         <v>-2.8502</v>
@@ -1312,13 +1312,13 @@
         <v>1.1585</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2702</v>
+        <v>0.855</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4686</v>
+        <v>0.7307</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1985</v>
+        <v>0.1243</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5133</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>19.4616</v>
+        <v>19.7376</v>
       </c>
       <c r="E12" t="n">
-        <v>13.3141</v>
+        <v>13.59</v>
       </c>
       <c r="F12" t="n">
-        <v>6.147399999999998</v>
+        <v>6.147399999999999</v>
       </c>
       <c r="G12" t="n">
         <v>7.828</v>
@@ -1390,13 +1390,13 @@
         <v>15.4462</v>
       </c>
       <c r="S12" t="n">
-        <v>10.7576</v>
+        <v>11.0334</v>
       </c>
       <c r="T12" t="n">
-        <v>4.548</v>
+        <v>4.8241</v>
       </c>
       <c r="U12" t="n">
-        <v>6.209300000000001</v>
+        <v>6.2095</v>
       </c>
       <c r="V12" t="n">
         <v>1.841600000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.9145</v>
+        <v>2.3723</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9799</v>
+        <v>2.1868</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0654</v>
+        <v>0.1856</v>
       </c>
       <c r="G13" t="n">
         <v>1.1971</v>
@@ -1468,13 +1468,13 @@
         <v>0.9654</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.1474</v>
+        <v>-0.6896</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5795</v>
+        <v>-0.3726</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5679</v>
+        <v>-0.3169</v>
       </c>
       <c r="V13" t="n">
         <v>0.8995</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.845</v>
+        <v>1.7623</v>
       </c>
       <c r="E14" t="n">
-        <v>2.3793</v>
+        <v>2.1725</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5343</v>
+        <v>-0.4102</v>
       </c>
       <c r="G14" t="n">
         <v>1.5515</v>
@@ -1546,13 +1546,13 @@
         <v>0.7723</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1933</v>
+        <v>-0.2759</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0825</v>
+        <v>-0.1244</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2757</v>
+        <v>-0.1516</v>
       </c>
       <c r="V14" t="n">
         <v>-0.2856</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1211</v>
+        <v>1.5003</v>
       </c>
       <c r="E15" t="n">
-        <v>3.4723</v>
+        <v>3.5757</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.3512</v>
+        <v>-2.0754</v>
       </c>
       <c r="G15" t="n">
         <v>2.8096</v>
@@ -1624,13 +1624,13 @@
         <v>1.1585</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0481</v>
+        <v>-0.6689000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3587</v>
+        <v>-0.2553</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6894</v>
+        <v>-0.4136</v>
       </c>
       <c r="V15" t="n">
         <v>-1.7989</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5321</v>
+        <v>1.2216</v>
       </c>
       <c r="E16" t="n">
         <v>0.671</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1388</v>
+        <v>0.5507</v>
       </c>
       <c r="G16" t="n">
         <v>1.6298</v>
@@ -1702,13 +1702,13 @@
         <v>2.3169</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.7928</v>
+        <v>-1.1033</v>
       </c>
       <c r="T16" t="n">
         <v>-0.8829</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9099</v>
+        <v>-0.2204</v>
       </c>
       <c r="V16" t="n">
         <v>-0.6565</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.8951</v>
+        <v>-0.5145</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.1623</v>
+        <v>0.0446</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7329</v>
+        <v>-0.5591</v>
       </c>
       <c r="G17" t="n">
         <v>-0.0552</v>
@@ -1780,13 +1780,13 @@
         <v>0.5792</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-0.3587</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.7174</v>
+        <v>-0.5105</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.022</v>
+        <v>0.1518</v>
       </c>
       <c r="V17" t="n">
         <v>0.2856</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9340000000000001</v>
+        <v>-0.756</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.7212</v>
+        <v>-0.6177</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2128</v>
+        <v>-0.1383</v>
       </c>
       <c r="G18" t="n">
         <v>-1.3795</v>
@@ -1858,13 +1858,13 @@
         <v>0.7723</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6124000000000001</v>
+        <v>-0.4345</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4415</v>
+        <v>-0.338</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1709</v>
+        <v>-0.0965</v>
       </c>
       <c r="V18" t="n">
         <v>0.2856</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5578</v>
+        <v>-0.9595</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0133</v>
+        <v>-0.8065</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5445</v>
+        <v>-0.153</v>
       </c>
       <c r="G19" t="n">
         <v>-0.5876</v>
@@ -1936,13 +1936,13 @@
         <v>2.51</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.074</v>
+        <v>-1.4757</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3796</v>
+        <v>-1.1727</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6945</v>
+        <v>-0.303</v>
       </c>
       <c r="V19" t="n">
         <v>2.4554</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. DEL CERRO RUIZ</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.5108</v>
+        <v>-3.6683</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.4085</v>
+        <v>-1.4672</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1022</v>
+        <v>-2.2011</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.4913</v>
+        <v>-2.5646</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.5856</v>
+        <v>-2.6551</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.9058</v>
+        <v>0.09039999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8552999999999999</v>
+        <v>0.2846</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4123</v>
+        <v>-1.5511</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.443</v>
+        <v>1.8357</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.636</v>
+        <v>-2.8492</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1733</v>
+        <v>-1.1039</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.4627</v>
+        <v>-1.7453</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3862</v>
+        <v>0.7723</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9308</v>
+        <v>-0.9654</v>
       </c>
       <c r="R20" t="n">
-        <v>2.3169</v>
+        <v>1.7377</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.7338</v>
+        <v>-0.6483</v>
       </c>
       <c r="T20" t="n">
-        <v>0.1925</v>
+        <v>-0.7864</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9263</v>
+        <v>0.1381</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3282</v>
+        <v>-1.2277</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1851</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.8568</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. IYOHA OSARENKHOE</t>
+          <t>D. DEL CERRO RUIZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0249</v>
+        <v>-3.8114</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8893</v>
+        <v>-2.2359</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1357</v>
+        <v>-1.5754</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.0895</v>
+        <v>-3.4913</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.1446</v>
+        <v>-1.5856</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.945</v>
+        <v>-1.9058</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.0064</v>
+        <v>-0.8552999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.0064</v>
+        <v>-0.4123</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.443</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.0832</v>
+        <v>-2.636</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1382</v>
+        <v>-1.1733</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.945</v>
+        <v>-1.4627</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.3862</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9654</v>
+        <v>-1.9308</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9654</v>
+        <v>2.3169</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2923</v>
+        <v>-1.0344</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0825</v>
+        <v>-0.6349</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2098</v>
+        <v>-0.3995</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2277</v>
+        <v>0.3282</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.1851</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2277</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>D. IYOHA OSARENKHOE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.2889</v>
+        <v>-4.2966</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6741</v>
+        <v>-3.1995</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.6148</v>
+        <v>-1.0971</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5646</v>
+        <v>-3.0895</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.6551</v>
+        <v>-2.1446</v>
       </c>
       <c r="I22" t="n">
-        <v>0.09039999999999999</v>
+        <v>-0.945</v>
       </c>
       <c r="J22" t="n">
-        <v>0.2846</v>
+        <v>-2.0064</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.5511</v>
+        <v>-2.0064</v>
       </c>
       <c r="L22" t="n">
-        <v>1.8357</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.8492</v>
+        <v>-1.0832</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.1039</v>
+        <v>-0.1382</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.7453</v>
+        <v>-0.945</v>
       </c>
       <c r="P22" t="n">
-        <v>0.7723</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R22" t="n">
-        <v>1.7377</v>
+        <v>0.9654</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2688</v>
+        <v>0.0206</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9933</v>
+        <v>-0.2278</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2756</v>
+        <v>0.2484</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2277</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>P. GRANJA I BERNAD</t>
+          <t>A. DELICADO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.7464</v>
+        <v>-4.3456</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.5596</v>
+        <v>-4.0148</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1868</v>
+        <v>-0.3309</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3877</v>
+        <v>-1.4604</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0073</v>
+        <v>-0.572</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.3804</v>
+        <v>-0.8885</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2355</v>
+        <v>1.1751</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0621</v>
+        <v>-0.0886</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2976</v>
+        <v>1.2637</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1522</v>
+        <v>-2.6355</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0693</v>
+        <v>-0.4833</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0829</v>
+        <v>-2.1522</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.5792</v>
+        <v>-2.8962</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9654</v>
+        <v>-4.827</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3862</v>
+        <v>1.9308</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5518</v>
+        <v>-0.3173</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3587</v>
+        <v>-0.6485</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.193</v>
+        <v>0.3313</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2277</v>
+        <v>0.3282</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2277</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. DELICADO DOMINGUEZ</t>
+          <t>P. GRANJA I BERNAD</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.9165</v>
+        <v>-4.5188</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.2216</v>
+        <v>-2.4562</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.6949</v>
+        <v>-2.0626</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.4604</v>
+        <v>-2.3877</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.572</v>
+        <v>-0.0073</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.8885</v>
+        <v>-2.3804</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1751</v>
+        <v>-1.2355</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.0886</v>
+        <v>0.0621</v>
       </c>
       <c r="L24" t="n">
-        <v>1.2637</v>
+        <v>-1.2976</v>
       </c>
       <c r="M24" t="n">
-        <v>-2.6355</v>
+        <v>-1.1522</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.4833</v>
+        <v>-0.0693</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.1522</v>
+        <v>-1.0829</v>
       </c>
       <c r="P24" t="n">
-        <v>-2.8962</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q24" t="n">
-        <v>-4.827</v>
+        <v>-0.9654</v>
       </c>
       <c r="R24" t="n">
-        <v>1.9308</v>
+        <v>0.3862</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.8881</v>
+        <v>-0.3242</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.8554</v>
+        <v>-0.2553</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0328</v>
+        <v>-0.0689</v>
       </c>
       <c r="V24" t="n">
-        <v>0.3282</v>
+        <v>-1.2277</v>
       </c>
       <c r="W24" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0.0426</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-19.4617</v>
+        <v>-16.0142</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.147399999999998</v>
+        <v>-6.147200000000002</v>
       </c>
       <c r="F25" t="n">
-        <v>-13.3143</v>
+        <v>-9.866800000000001</v>
       </c>
       <c r="G25" t="n">
         <v>-7.8278</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3442000000000003</v>
+        <v>0.3441999999999998</v>
       </c>
       <c r="I25" t="n">
         <v>-8.1724</v>
@@ -2380,7 +2380,7 @@
         <v>10.768</v>
       </c>
       <c r="K25" t="n">
-        <v>6.902000000000002</v>
+        <v>6.902000000000001</v>
       </c>
       <c r="L25" t="n">
         <v>3.8662</v>
@@ -2395,7 +2395,7 @@
         <v>-12.0387</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9653999999999994</v>
+        <v>0.9653999999999995</v>
       </c>
       <c r="Q25" t="n">
         <v>-15.4464</v>
@@ -2404,13 +2404,13 @@
         <v>16.4116</v>
       </c>
       <c r="S25" t="n">
-        <v>-10.7576</v>
+        <v>-7.310200000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-6.2095</v>
+        <v>-6.209300000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>-4.548199999999999</v>
+        <v>-1.1008</v>
       </c>
       <c r="V25" t="n">
         <v>-1.8416</v>
@@ -2419,7 +2419,7 @@
         <v>4.7403</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.581800000000001</v>
+        <v>-6.581799999999999</v>
       </c>
     </row>
   </sheetData>
